--- a/public/seller-template.xlsx
+++ b/public/seller-template.xlsx
@@ -48,12 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0015803D"/>
+        <fgColor rgb="003F3F46"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003F3F46"/>
+        <fgColor rgb="0015803D"/>
       </patternFill>
     </fill>
   </fills>
@@ -159,90 +159,115 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Required. Just the number, e.g. 450000. RM 450,000 also works.</t>
+        <t>Optional. Sale or Rent. Blank means sale. Long-term rentals only: 6 months or more. No holiday lets or short stays.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
+        <t>Required. Just the number, e.g. 450000 (or the monthly rent, e.g. 2500). RM 450,000 also works.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
         <t>Required. Town and country, e.g. Ipoh, Perak, Malaysia. Or leave blank and fill Latitude and Longitude.</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Required. Shown to buyers so they know who they're talking to.</t>
-      </text>
-    </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Optional. With country code if you can, e.g. +60 12 345 6789. Buyers call or WhatsApp you.</t>
+        <t>Required. Shown to buyers and tenants so they know who they're talking to.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Optional. Buyers can email you.</t>
+        <t>Optional. With country code if you can, e.g. +60 12 345 6789.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
+        <t>Optional. Buyers and tenants can email you.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
         <t>Optional. MYR, SGD, AUD, GBP… Worked out from the location if left blank.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Optional. House, Condominium, Apartment, Terrace, Bungalow, Land…</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Optional. A number. Studio = 0.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Optional. A number.</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Optional. A number, e.g. 1200. Put the unit in Area unit.</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Optional. A number, for houses and land.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>Optional. sq ft, sq m, acres or hectares.</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>Optional. Freehold, Leasehold, or your local term.</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Rentals only: the deposit amount.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Rentals only: Furnished, Partly furnished or Unfurnished.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Rentals only: a date, or Now.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Rentals only: 6 or more.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Optional. A short title. Leave blank and we write one, e.g. 3-bedroom house in Ipoh.</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional. Anything buyers should know.</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Anything buyers or tenants should know.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>Optional. Links to photos already online (https://…), separated by spaces. Or add photos from your phone with the one-page form instead.</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>Optional. Map pin, e.g. 4.5975. Tip: in Google Maps, press and hold on your home and copy the numbers.</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>Optional. Map pin, e.g. 101.0901.</t>
       </text>
@@ -540,125 +565,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>For sale or rent</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>Asking price</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Your name</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Phone or WhatsApp</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property type</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Bedrooms</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bathrooms</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Floor area</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Land size</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Area unit</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Tenure</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Furnished</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Available from</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Minimum lease (months)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Headline</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Photo links</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sale,Rent"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"sq ft,sq m,acres,hectares"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Furnished,Partly furnished,Unfurnished"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -672,10 +733,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
@@ -690,65 +751,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>One property per row on the Listings tab. Only the green columns are needed. Save, then upload at sellmyhouse.asia/upload. Free, no account.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+          <t>One property per row on the Listings tab (only that tab is read). Save, then upload at sellmyhouse.asia/upload. Free, no account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Long-term rentals only: 6 months or more. No holiday lets or short stays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Needed?</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>What to put in it</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Asking price</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Just the number, e.g. 450000. RM 450,000 also works.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>For sale or rent</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Town and country, e.g. Ipoh, Perak, Malaysia. Or leave blank and fill Latitude and Longitude.</t>
+          <t>Sale or Rent. Blank means sale. Long-term rentals only: 6 months or more. No holiday lets or short stays.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Your name</t>
+          <t>Asking price</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -758,48 +809,48 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shown to buyers so they know who they're talking to.</t>
+          <t>Just the number, e.g. 450000 (or the monthly rent, e.g. 2500). RM 450,000 also works.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Phone or WhatsApp</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>With country code if you can, e.g. +60 12 345 6789. Buyers call or WhatsApp you.</t>
+          <t>Town and country, e.g. Ipoh, Perak, Malaysia. Or leave blank and fill Latitude and Longitude.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Your name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Buyers can email you.</t>
+          <t>Shown to buyers and tenants so they know who they're talking to.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Phone or WhatsApp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -809,14 +860,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MYR, SGD, AUD, GBP… Worked out from the location if left blank.</t>
+          <t>With country code if you can, e.g. +60 12 345 6789.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Property type</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -826,14 +877,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>House, Condominium, Apartment, Terrace, Bungalow, Land…</t>
+          <t>Buyers and tenants can email you.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bedrooms</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -843,14 +894,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A number. Studio = 0.</t>
+          <t>MYR, SGD, AUD, GBP… Worked out from the location if left blank.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bathrooms</t>
+          <t>Property type</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -860,14 +911,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A number.</t>
+          <t>House, Condominium, Apartment, Terrace, Bungalow, Land…</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Floor area</t>
+          <t>Bedrooms</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -877,14 +928,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A number, e.g. 1200. Put the unit in Area unit.</t>
+          <t>A number. Studio = 0.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Land size</t>
+          <t>Bathrooms</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -894,14 +945,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A number, for houses and land.</t>
+          <t>A number.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Area unit</t>
+          <t>Floor area</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -911,14 +962,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sq ft, sq m, acres or hectares.</t>
+          <t>A number, e.g. 1200. Put the unit in Area unit.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tenure</t>
+          <t>Land size</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -928,14 +979,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Freehold, Leasehold, or your local term.</t>
+          <t>A number, for houses and land.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Area unit</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -945,14 +996,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A short title. Leave blank and we write one, e.g. 3-bedroom house in Ipoh.</t>
+          <t>sq ft, sq m, acres or hectares.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Tenure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -962,14 +1013,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Anything buyers should know.</t>
+          <t>Freehold, Leasehold, or your local term.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Photo links</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -979,14 +1030,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Links to photos already online (https://…), separated by spaces. Or add photos from your phone with the one-page form instead.</t>
+          <t>Rentals only: the deposit amount.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Furnished</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -996,22 +1047,124 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Map pin, e.g. 4.5975. Tip: in Google Maps, press and hold on your home and copy the numbers.</t>
+          <t>Rentals only: Furnished, Partly furnished or Unfurnished.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Available from</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rentals only: a date, or Now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Minimum lease (months)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rentals only: 6 or more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A short title. Leave blank and we write one, e.g. 3-bedroom house in Ipoh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Anything buyers or tenants should know.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Photo links</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Links to photos already online (https://…), separated by spaces. Or add photos from your phone with the one-page form instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Map pin, e.g. 4.5975. Tip: in Google Maps, press and hold on your home and copy the numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Map pin, e.g. 101.0901.</t>
         </is>
@@ -1028,168 +1181,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>For sale or rent</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>Asking price</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Your name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Phone or WhatsApp</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Property type</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Bedrooms</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Bathrooms</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Floor area</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Land size</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Area unit</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Tenure</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Furnished</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Available from</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Minimum lease (months)</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Headline</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Photo links</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
         <is>
           <t>450000</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ipoh, Perak, Malaysia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>+60 12 345 6789</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Terrace</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>1650</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>sq ft</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Freehold</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Corner unit, renovated kitchen, near schools.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
         <is>
           <t>4.5975</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>101.0901</t>
         </is>
